--- a/data/trans_orig/P79_n_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R3-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>51817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>75857</t>
+          <t>87684</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61692</t>
+          <t>72580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91759</t>
+          <t>104084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -951,67 +951,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>111956</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>97937</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>129123</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>13,62%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97801</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84633</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112553</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>154359</t>
+          <t>181483</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>161269</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171736</t>
+          <t>205071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>420950</t>
+          <t>466134</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>403121</t>
+          <t>444911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>434855</t>
+          <t>483401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607587</t>
+          <t>652566</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>590448</t>
+          <t>633712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>624204</t>
+          <t>667902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1028537</t>
+          <t>1118700</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1004966</t>
+          <t>1090688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1052705</t>
+          <t>1144247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>76165</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>59534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83621</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>73763</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80876</t>
+          <t>95507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>125764</t>
+          <t>149928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>123764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>177035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>232991</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140425</t>
+          <t>199862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243379</t>
+          <t>272348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>184941</t>
+          <t>217861</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140359</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219301</t>
+          <t>244424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>385546</t>
+          <t>450853</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310532</t>
+          <t>409843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>495281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2008621</t>
+          <t>1903133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1955073</t>
+          <t>1859626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2101140</t>
+          <t>1942315</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1979250</t>
+          <t>1868423</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1932984</t>
+          <t>1836974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2042174</t>
+          <t>1898376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3987871</t>
+          <t>3771556</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3914673</t>
+          <t>3720164</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4100782</t>
+          <t>3819889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,92 +1873,92 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7589</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3534</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7313</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39697</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>55079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>89617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>612087</t>
+          <t>670228</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597063</t>
+          <t>654723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623505</t>
+          <t>682803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>620146</t>
+          <t>688482</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>606743</t>
+          <t>674930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>629828</t>
+          <t>699916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1232233</t>
+          <t>1358710</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212794</t>
+          <t>1338354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246574</t>
+          <t>1375027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,22 +2467,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63524</t>
+          <t>62953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78747</t>
+          <t>100929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129013</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>108767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>153724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179626</t>
+          <t>223371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>286915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>226246</t>
+          <t>299685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>327792</t>
+          <t>377281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>258958</t>
+          <t>334846</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>354373</t>
+          <t>402453</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>652061</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>661701</t>
+          <t>757067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3041659</t>
+          <t>3039495</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2986391</t>
+          <t>2993778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3123314</t>
+          <t>3082274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3206983</t>
+          <t>3209471</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3159785</t>
+          <t>3169161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3288379</t>
+          <t>3250825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6248642</t>
+          <t>6248966</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6171997</t>
+          <t>6185945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6363109</t>
+          <t>6308929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
